--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18AB624A-1776-445B-BFE9-90C846308EBA}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78308F1D-E7E1-4D4B-817F-D3FD30C3848F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
-        <v>2026</v>
+        <v>46280</v>
       </c>
       <c r="B7" s="14">
         <v>500</v>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78308F1D-E7E1-4D4B-817F-D3FD30C3848F}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE40873A-512D-496D-A232-40F327D34A9C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1084,25 +1084,47 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>510</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE40873A-512D-496D-A232-40F327D34A9C}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13A5E2CF-5160-4572-82E9-9643172605EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>Felt tired in night</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -1128,26 +1131,50 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>80</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>630</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13A5E2CF-5160-4572-82E9-9643172605EF}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE47B1B-8AFC-4D9E-B0E2-B02085974CCC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -498,6 +498,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1116,8 +1120,7 @@
         <v>1440</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>49</v>
@@ -1160,8 +1163,7 @@
         <v>1440</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>56</v>
@@ -1177,26 +1179,49 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>50</v>
+      </c>
+      <c r="D10" s="14">
+        <v>150</v>
+      </c>
+      <c r="E10" s="14">
+        <v>70</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>470</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>1440</v>
+      </c>
+      <c r="J10" s="15">
+        <v>470</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDE47B1B-8AFC-4D9E-B0E2-B02085974CCC}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4749B3E3-444F-40CE-9377-6285F4894941}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>2026-0919</t>
   </si>
 </sst>
 </file>
@@ -1224,26 +1227,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="14">
+        <v>450</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>80</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>650</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4749B3E3-444F-40CE-9377-6285F4894941}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DBB6A4A-E89F-413B-93F3-C04222D3B75B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,7 +220,7 @@
     <t>good</t>
   </si>
   <si>
-    <t>2026-0919</t>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1227,8 +1227,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>61</v>
+      <c r="A11" s="13">
+        <v>46284</v>
       </c>
       <c r="B11" s="14">
         <v>450</v>
@@ -1273,26 +1273,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>50</v>
+      </c>
+      <c r="D12" s="14">
+        <v>200</v>
+      </c>
+      <c r="E12" s="14">
+        <v>70</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>670</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DBB6A4A-E89F-413B-93F3-C04222D3B75B}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE505BC9-0015-430B-A50C-2CFF94FBF9F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>Unsatisfied</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Felt tired in night</t>
@@ -1087,10 +1084,10 @@
         <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1178,7 +1175,7 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1223,7 +1220,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1269,7 +1266,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1306,39 +1303,63 @@
         <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>80</v>
+      </c>
+      <c r="D13" s="14">
+        <v>220</v>
+      </c>
+      <c r="E13" s="14">
+        <v>80</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>400</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE505BC9-0015-430B-A50C-2CFF94FBF9F1}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57C1D276-2F29-4723-9F5D-7D1F8D23A828}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1362,26 +1362,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B14" s="14">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>90</v>
+      </c>
+      <c r="D14" s="14">
+        <v>230</v>
+      </c>
+      <c r="E14" s="14">
+        <v>80</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>380</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57C1D276-2F29-4723-9F5D-7D1F8D23A828}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F3B3A2-4943-420F-A506-851DCD5EDF87}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1408,26 +1408,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B15" s="14">
+        <v>400</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>250</v>
+      </c>
+      <c r="E15" s="14">
+        <v>70</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>360</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F3B3A2-4943-420F-A506-851DCD5EDF87}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098396DB-C6AC-41F3-B13F-28D12749D13A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1454,26 +1454,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>80</v>
+      </c>
+      <c r="D16" s="14">
+        <v>250</v>
+      </c>
+      <c r="E16" s="14">
+        <v>80</v>
+      </c>
+      <c r="F16" s="14">
+        <v>150</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16" s="14">
+        <v>430</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098396DB-C6AC-41F3-B13F-28D12749D13A}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84326B78-EA65-4A71-BAB0-6024A823C054}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1500,26 +1503,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>90</v>
+      </c>
+      <c r="D17" s="14">
+        <v>300</v>
+      </c>
+      <c r="E17" s="14">
+        <v>80</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>220</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84326B78-EA65-4A71-BAB0-6024A823C054}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6218A36E-C9C6-4002-A507-B265B43DE6BB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1549,26 +1549,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>90</v>
+      </c>
+      <c r="D18" s="14">
+        <v>300</v>
+      </c>
+      <c r="E18" s="14">
+        <v>80</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>520</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6218A36E-C9C6-4002-A507-B265B43DE6BB}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE71A4C9-08CB-4589-9346-04F8E38EEF7C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1595,26 +1595,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
+      <c r="C19" s="14">
+        <v>90</v>
+      </c>
+      <c r="D19" s="14">
+        <v>250</v>
+      </c>
+      <c r="E19" s="14">
+        <v>80</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>720</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE71A4C9-08CB-4589-9346-04F8E38EEF7C}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA6E370C-CF08-4E64-A77A-3B8DEDFC2D30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>feeling not well</t>
   </si>
 </sst>
 </file>
@@ -1641,26 +1644,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>250</v>
+      </c>
+      <c r="E20" s="14">
+        <v>70</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>770</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA6E370C-CF08-4E64-A77A-3B8DEDFC2D30}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D08D5C-D994-4405-B114-83DBEF041A6A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>feeling not well</t>
+  </si>
+  <si>
+    <t>IF(K1821=I25"","",1440-I21)</t>
   </si>
 </sst>
 </file>
@@ -1689,27 +1692,50 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="28" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>90</v>
+      </c>
+      <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>70</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>620</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>1440</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D08D5C-D994-4405-B114-83DBEF041A6A}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45969B73-E426-46BB-A03A-B0DDFD7FACC7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,7 +226,7 @@
     <t>feeling not well</t>
   </si>
   <si>
-    <t>IF(K1821=I25"","",1440-I21)</t>
+    <t>not good</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="28" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46294</v>
       </c>
@@ -1721,8 +1721,8 @@
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J21" s="15" t="s">
-        <v>63</v>
+      <c r="J21" s="15">
+        <v>0</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>56</v>
@@ -1738,26 +1738,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>90</v>
+      </c>
+      <c r="D22" s="14">
+        <v>250</v>
+      </c>
+      <c r="E22" s="14">
+        <v>80</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>600</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45969B73-E426-46BB-A03A-B0DDFD7FACC7}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D866B89C-6D71-4EB3-92A0-B6D8A85A285D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1784,26 +1784,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>80</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>80</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>530</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D866B89C-6D71-4EB3-92A0-B6D8A85A285D}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F2362B5-A4AA-40C7-9819-CBA2D4152C35}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1830,26 +1830,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>100</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>80</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>510</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F2362B5-A4AA-40C7-9819-CBA2D4152C35}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{143064EA-CD80-4F15-9146-23049906C602}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,9 +214,6 @@
     <t>Felt tired in night</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
   </si>
   <si>
     <t>not good</t>
+  </si>
+  <si>
+    <t>GOOD</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1093,7 @@
         <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>58</v>
@@ -1184,7 +1184,7 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1229,7 +1229,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1275,7 +1275,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1312,16 +1312,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1367,7 +1367,7 @@
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1413,7 +1413,7 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1459,7 +1459,7 @@
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -1505,7 +1505,7 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -1548,10 +1548,10 @@
         <v>50</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -1594,10 +1594,10 @@
         <v>57</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -1643,7 +1643,7 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -1680,16 +1680,16 @@
         <v>0</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1734,7 +1734,7 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1780,7 +1780,7 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -1826,7 +1826,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -1869,33 +1869,57 @@
         <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B25" s="14">
+        <v>400</v>
+      </c>
+      <c r="C25" s="14">
+        <v>80</v>
+      </c>
+      <c r="D25" s="14">
+        <v>200</v>
+      </c>
+      <c r="E25" s="14">
+        <v>70</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>690</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{143064EA-CD80-4F15-9146-23049906C602}"/>
+  <xr:revisionPtr revIDLastSave="285" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4F40D3-B943-4072-A347-81FB906AE513}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>not good</t>
-  </si>
-  <si>
-    <t>GOOD</t>
   </si>
 </sst>
 </file>
@@ -1918,30 +1915,54 @@
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B26" s="14">
+        <v>200</v>
+      </c>
+      <c r="C26" s="14">
+        <v>70</v>
+      </c>
+      <c r="D26" s="14">
+        <v>200</v>
+      </c>
+      <c r="E26" s="14">
+        <v>100</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>870</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4F40D3-B943-4072-A347-81FB906AE513}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A205AF7-7AC2-4A4B-81E6-7AF992E8F279}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1965,26 +1965,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>150</v>
+      </c>
+      <c r="E27" s="14">
+        <v>80</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>400</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A205AF7-7AC2-4A4B-81E6-7AF992E8F279}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC9DCEC-8DEF-4E60-B1F5-26BB3F33D297}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2011,26 +2011,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>80</v>
+      </c>
+      <c r="D28" s="14">
+        <v>150</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>430</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC9DCEC-8DEF-4E60-B1F5-26BB3F33D297}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11DF777A-68B3-48E3-A11E-AF5E81D79557}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2057,26 +2057,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B29" s="14">
+        <v>450</v>
+      </c>
+      <c r="C29" s="14">
+        <v>70</v>
+      </c>
+      <c r="D29" s="14">
+        <v>150</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>410</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11DF777A-68B3-48E3-A11E-AF5E81D79557}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E49277-06D7-4CF9-8565-B36DD6581DA4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2103,26 +2103,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B30" s="14">
+        <v>450</v>
+      </c>
+      <c r="C30" s="14">
+        <v>80</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>580</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12628971.xlsx
+++ b/12628971.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/909b850e38486718/Desktop/12628971CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E49277-06D7-4CF9-8565-B36DD6581DA4}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA91C37D-D75B-4461-84A2-E517BAE5DF98}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -878,7 +878,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N424"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1030,11 +1030,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I92" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J92" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1051,8 +1051,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
-        <v>46280</v>
+      <c r="A7" s="8">
+        <v>46251</v>
       </c>
       <c r="B7" s="14">
         <v>500</v>
@@ -1076,11 +1076,11 @@
         <v>20</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>970</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I7="","",1440-I7)</f>
         <v>470</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1093,1566 +1093,1458 @@
         <v>59</v>
       </c>
       <c r="N7" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B30" s="14">
+        <v>500</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>100</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>20</v>
+      </c>
+      <c r="I30" s="15">
+        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>970</v>
+      </c>
+      <c r="J30" s="15">
+        <f>IF(I30="","",1440-I30)</f>
+        <v>470</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
         <v>46281</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B31" s="14">
         <v>420</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C31" s="14">
         <v>30</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D31" s="14">
         <v>120</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E31" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F31" s="14">
         <v>300</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G31" s="14">
         <v>5</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H31" s="14">
         <v>510</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J31" s="15">
         <v>510</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K31" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
+      <c r="N31" s="17"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
         <v>46282</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B32" s="14">
         <v>420</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C32" s="14">
         <v>40</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D32" s="14">
         <v>120</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E32" s="14">
         <v>80</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F32" s="14">
         <v>150</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G32" s="14">
         <v>3</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H32" s="14">
         <v>630</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J32" s="15">
         <v>630</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K32" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M32" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N32" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
         <v>46283</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B33" s="14">
         <v>400</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C33" s="14">
         <v>50</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D33" s="14">
         <v>150</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E33" s="14">
         <v>70</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F33" s="14">
         <v>300</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G33" s="14">
         <v>6</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H33" s="14">
         <v>470</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J33" s="15">
         <v>470</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K33" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L33" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N33" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
         <v>46284</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B34" s="14">
         <v>450</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C34" s="14">
         <v>60</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D34" s="14">
         <v>200</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E34" s="14">
         <v>80</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F34" s="14">
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G34" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H34" s="14">
         <v>650</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K34" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N34" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
         <v>46285</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B35" s="14">
         <v>450</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C35" s="14">
         <v>50</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D35" s="14">
         <v>200</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E35" s="14">
         <v>70</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F35" s="14">
         <v>0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G35" s="14">
         <v>0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H35" s="14">
         <v>670</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K35" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L35" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M35" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N35" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
         <v>46286</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B36" s="14">
         <v>360</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C36" s="14">
         <v>80</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D36" s="14">
         <v>220</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E36" s="14">
         <v>80</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F36" s="14">
         <v>300</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G36" s="14">
         <v>6</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H36" s="14">
         <v>400</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K36" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L36" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M36" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N36" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
         <v>46287</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B37" s="14">
         <v>360</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C37" s="14">
         <v>90</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D37" s="14">
         <v>230</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E37" s="14">
         <v>80</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F37" s="14">
         <v>300</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G37" s="14">
         <v>6</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H37" s="14">
         <v>380</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K37" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L37" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N37" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
         <v>46288</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B38" s="14">
         <v>400</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C38" s="14">
         <v>60</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D38" s="14">
         <v>250</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E38" s="14">
         <v>70</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F38" s="14">
         <v>300</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G38" s="14">
         <v>6</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H38" s="14">
         <v>360</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K38" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L38" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M38" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N38" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
         <v>46289</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B39" s="14">
         <v>450</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C39" s="14">
         <v>80</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D39" s="14">
         <v>250</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E39" s="14">
         <v>80</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F39" s="14">
         <v>150</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H39" s="14">
         <v>430</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K39" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L39" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N39" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
         <v>46290</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B40" s="14">
         <v>450</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C40" s="14">
         <v>90</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D40" s="14">
         <v>300</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E40" s="14">
         <v>80</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F40" s="14">
         <v>300</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G40" s="14">
         <v>6</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H40" s="14">
         <v>220</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K40" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N40" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
         <v>46291</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B41" s="14">
         <v>450</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C41" s="14">
         <v>90</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D41" s="14">
         <v>300</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E41" s="14">
         <v>80</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F41" s="14">
         <v>0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G41" s="14">
         <v>0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H41" s="14">
         <v>520</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K41" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L41" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M41" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N41" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
         <v>46292</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B42" s="14">
         <v>300</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C42" s="14">
         <v>90</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D42" s="14">
         <v>250</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E42" s="14">
         <v>80</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F42" s="14">
         <v>0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G42" s="14">
         <v>0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H42" s="14">
         <v>720</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K42" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L42" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M42" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N42" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
         <v>46293</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B43" s="14">
         <v>300</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C43" s="14">
         <v>50</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D43" s="14">
         <v>250</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E43" s="14">
         <v>70</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F43" s="14">
         <v>0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G43" s="14">
         <v>0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H43" s="14">
         <v>770</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K43" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L43" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M43" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N43" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
         <v>46294</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B44" s="14">
         <v>420</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C44" s="14">
         <v>90</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D44" s="14">
         <v>240</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E44" s="14">
         <v>70</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F44" s="14">
         <v>0</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G44" s="14">
         <v>0</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H44" s="14">
         <v>620</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J44" s="15">
         <v>0</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K44" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L44" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M21" s="16" t="s">
+      <c r="M44" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N44" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
         <v>46295</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B45" s="14">
         <v>420</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C45" s="14">
         <v>90</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D45" s="14">
         <v>250</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E45" s="14">
         <v>80</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F45" s="14">
         <v>0</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G45" s="14">
         <v>0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H45" s="14">
         <v>600</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K45" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L45" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M45" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N45" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
         <v>46296</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B46" s="14">
         <v>450</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C46" s="14">
         <v>80</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D46" s="14">
         <v>300</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E46" s="14">
         <v>80</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F46" s="14">
         <v>0</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G46" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H46" s="14">
         <v>530</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K46" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L46" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M46" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N46" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" s="13">
         <v>46297</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B47" s="14">
         <v>450</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C47" s="14">
         <v>100</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D47" s="14">
         <v>300</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E47" s="14">
         <v>80</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F47" s="14">
         <v>0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G47" s="14">
         <v>0</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H47" s="14">
         <v>510</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K47" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="16" t="s">
+      <c r="L47" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="M47" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N47" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
         <v>46298</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B48" s="14">
         <v>400</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C48" s="14">
         <v>80</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D48" s="14">
         <v>200</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E48" s="14">
         <v>70</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F48" s="14">
         <v>0</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G48" s="14">
         <v>0</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H48" s="14">
         <v>690</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K48" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L25" s="16" t="s">
+      <c r="L48" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M48" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N48" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
         <v>46299</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B49" s="14">
         <v>200</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C49" s="14">
         <v>70</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D49" s="14">
         <v>200</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E49" s="14">
         <v>100</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F49" s="14">
         <v>0</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G49" s="14">
         <v>0</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H49" s="14">
         <v>870</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K49" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="L49" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M49" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N49" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
         <v>46300</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B50" s="14">
         <v>450</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C50" s="14">
         <v>60</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D50" s="14">
         <v>150</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E50" s="14">
         <v>80</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F50" s="14">
         <v>300</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G50" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H50" s="14">
         <v>400</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K50" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="L50" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M50" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N27" s="17" t="s">
+      <c r="N50" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
         <v>46301</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B51" s="14">
         <v>420</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C51" s="14">
         <v>80</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D51" s="14">
         <v>150</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E51" s="14">
         <v>60</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F51" s="14">
         <v>300</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G51" s="14">
         <v>6</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H51" s="14">
         <v>430</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K51" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L28" s="16" t="s">
+      <c r="L51" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M28" s="16" t="s">
+      <c r="M51" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N51" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
         <v>46302</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B52" s="14">
         <v>450</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C52" s="14">
         <v>70</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D52" s="14">
         <v>150</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E52" s="14">
         <v>60</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F52" s="14">
         <v>300</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G52" s="14">
         <v>6</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H52" s="14">
         <v>410</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K52" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L52" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M52" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N52" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
         <v>46303</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B53" s="14">
         <v>450</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C53" s="14">
         <v>80</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D53" s="14">
         <v>120</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E53" s="14">
         <v>60</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F53" s="14">
         <v>150</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G53" s="14">
         <v>3</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H53" s="14">
         <v>580</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
         <v>1440</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K53" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L30" s="16" t="s">
+      <c r="L53" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M53" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N30" s="17" t="s">
+      <c r="N53" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
@@ -3016,11 +2908,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3038,11 +2930,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3060,11 +2952,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3082,11 +2974,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3104,11 +2996,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3126,11 +3018,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3148,11 +3040,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3170,11 +3062,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3192,11 +3084,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3214,11 +3106,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3236,11 +3128,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3258,11 +3150,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3280,11 +3172,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3302,11 +3194,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3324,11 +3216,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3346,11 +3238,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3368,11 +3260,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3390,11 +3282,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3412,11 +3304,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3434,11 +3326,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3456,11 +3348,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3478,11 +3370,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3500,11 +3392,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3522,11 +3414,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I93:I156" si="2">IF(SUM(B93:F93,H93)=0,"",SUM(B93:F93,H93))</f>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J93:J156" si="3">IF(I93="","",1440-I93)</f>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4424,11 +4316,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4446,11 +4338,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4468,11 +4360,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4490,11 +4382,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4512,11 +4404,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4534,11 +4426,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4556,11 +4448,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4578,11 +4470,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4600,11 +4492,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4622,11 +4514,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4644,11 +4536,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4666,11 +4558,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4688,11 +4580,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4710,11 +4602,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4732,11 +4624,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4754,11 +4646,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4776,11 +4668,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4798,11 +4690,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4820,11 +4712,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4842,11 +4734,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4864,11 +4756,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4886,11 +4778,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4908,11 +4800,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4930,11 +4822,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I157:I220" si="4">IF(SUM(B157:F157,H157)=0,"",SUM(B157:F157,H157))</f>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J157:J220" si="5">IF(I157="","",1440-I157)</f>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5832,11 +5724,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5854,11 +5746,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5876,11 +5768,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5898,11 +5790,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5920,11 +5812,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5942,11 +5834,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5964,11 +5856,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5986,11 +5878,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6008,11 +5900,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6030,11 +5922,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6052,11 +5944,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6074,11 +5966,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6096,11 +5988,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6118,11 +6010,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6140,11 +6032,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6162,11 +6054,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6184,11 +6076,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6206,11 +6098,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6228,11 +6120,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6250,11 +6142,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6272,11 +6164,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6294,11 +6186,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6316,11 +6208,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6338,11 +6230,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I221:I284" si="6">IF(SUM(B221:F221,H221)=0,"",SUM(B221:F221,H221))</f>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J221:J284" si="7">IF(I221="","",1440-I221)</f>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7240,11 +7132,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7262,11 +7154,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7284,11 +7176,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7306,11 +7198,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7328,11 +7220,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7350,11 +7242,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7372,11 +7264,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7394,11 +7286,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7416,11 +7308,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7438,11 +7330,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7460,11 +7352,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7482,11 +7374,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7504,11 +7396,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7526,11 +7418,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7548,11 +7440,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7570,11 +7462,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7592,11 +7484,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7614,11 +7506,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7636,11 +7528,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7658,11 +7550,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7680,11 +7572,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7702,11 +7594,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7724,11 +7616,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7746,11 +7638,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I285:I348" si="8">IF(SUM(B285:F285,H285)=0,"",SUM(B285:F285,H285))</f>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J285:J348" si="9">IF(I285="","",1440-I285)</f>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8648,11 +8540,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8670,11 +8562,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8692,11 +8584,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8714,11 +8606,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8736,11 +8628,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8758,11 +8650,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8780,11 +8672,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8802,11 +8694,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8824,11 +8716,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8846,11 +8738,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8868,11 +8760,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8890,11 +8782,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8912,11 +8804,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8934,11 +8826,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8956,11 +8848,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8978,11 +8870,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9000,11 +8892,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9022,11 +8914,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9044,11 +8936,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9066,11 +8958,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9088,11 +8980,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9110,11 +9002,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9132,11 +9024,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9154,11 +9046,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I349:I412" si="10">IF(SUM(B349:F349,H349)=0,"",SUM(B349:F349,H349))</f>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J349:J412" si="11">IF(I349="","",1440-I349)</f>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10056,11 +9948,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10078,11 +9970,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10100,11 +9992,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10122,11 +10014,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10144,11 +10036,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10166,11 +10058,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10188,11 +10080,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10210,11 +10102,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10232,11 +10124,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10254,11 +10146,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10276,11 +10168,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10298,17 +10190,523 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
       <c r="L401" s="16"/>
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A406" s="13"/>
+      <c r="B406" s="14"/>
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J406" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K406" s="16"/>
+      <c r="L406" s="16"/>
+      <c r="M406" s="16"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A407" s="13"/>
+      <c r="B407" s="14"/>
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J407" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K407" s="16"/>
+      <c r="L407" s="16"/>
+      <c r="M407" s="16"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A408" s="13"/>
+      <c r="B408" s="14"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J408" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K408" s="16"/>
+      <c r="L408" s="16"/>
+      <c r="M408" s="16"/>
+      <c r="N408" s="17"/>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A409" s="13"/>
+      <c r="B409" s="14"/>
+      <c r="C409" s="14"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="14"/>
+      <c r="F409" s="14"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="I409" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J409" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K409" s="16"/>
+      <c r="L409" s="16"/>
+      <c r="M409" s="16"/>
+      <c r="N409" s="17"/>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A410" s="13"/>
+      <c r="B410" s="14"/>
+      <c r="C410" s="14"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="14"/>
+      <c r="F410" s="14"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="I410" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J410" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K410" s="16"/>
+      <c r="L410" s="16"/>
+      <c r="M410" s="16"/>
+      <c r="N410" s="17"/>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A411" s="13"/>
+      <c r="B411" s="14"/>
+      <c r="C411" s="14"/>
+      <c r="D411" s="14"/>
+      <c r="E411" s="14"/>
+      <c r="F411" s="14"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="I411" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J411" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K411" s="16"/>
+      <c r="L411" s="16"/>
+      <c r="M411" s="16"/>
+      <c r="N411" s="17"/>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A412" s="13"/>
+      <c r="B412" s="14"/>
+      <c r="C412" s="14"/>
+      <c r="D412" s="14"/>
+      <c r="E412" s="14"/>
+      <c r="F412" s="14"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="I412" s="15" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J412" s="15" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K412" s="16"/>
+      <c r="L412" s="16"/>
+      <c r="M412" s="16"/>
+      <c r="N412" s="17"/>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A413" s="13"/>
+      <c r="B413" s="14"/>
+      <c r="C413" s="14"/>
+      <c r="D413" s="14"/>
+      <c r="E413" s="14"/>
+      <c r="F413" s="14"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="I413" s="15" t="str">
+        <f t="shared" ref="I413:I424" si="12">IF(SUM(B413:F413,H413)=0,"",SUM(B413:F413,H413))</f>
+        <v/>
+      </c>
+      <c r="J413" s="15" t="str">
+        <f t="shared" ref="J413:J424" si="13">IF(I413="","",1440-I413)</f>
+        <v/>
+      </c>
+      <c r="K413" s="16"/>
+      <c r="L413" s="16"/>
+      <c r="M413" s="16"/>
+      <c r="N413" s="17"/>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A414" s="13"/>
+      <c r="B414" s="14"/>
+      <c r="C414" s="14"/>
+      <c r="D414" s="14"/>
+      <c r="E414" s="14"/>
+      <c r="F414" s="14"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="I414" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J414" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K414" s="16"/>
+      <c r="L414" s="16"/>
+      <c r="M414" s="16"/>
+      <c r="N414" s="17"/>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A415" s="13"/>
+      <c r="B415" s="14"/>
+      <c r="C415" s="14"/>
+      <c r="D415" s="14"/>
+      <c r="E415" s="14"/>
+      <c r="F415" s="14"/>
+      <c r="G415" s="14"/>
+      <c r="H415" s="14"/>
+      <c r="I415" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J415" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K415" s="16"/>
+      <c r="L415" s="16"/>
+      <c r="M415" s="16"/>
+      <c r="N415" s="17"/>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A416" s="13"/>
+      <c r="B416" s="14"/>
+      <c r="C416" s="14"/>
+      <c r="D416" s="14"/>
+      <c r="E416" s="14"/>
+      <c r="F416" s="14"/>
+      <c r="G416" s="14"/>
+      <c r="H416" s="14"/>
+      <c r="I416" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J416" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K416" s="16"/>
+      <c r="L416" s="16"/>
+      <c r="M416" s="16"/>
+      <c r="N416" s="17"/>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A417" s="13"/>
+      <c r="B417" s="14"/>
+      <c r="C417" s="14"/>
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+      <c r="F417" s="14"/>
+      <c r="G417" s="14"/>
+      <c r="H417" s="14"/>
+      <c r="I417" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J417" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K417" s="16"/>
+      <c r="L417" s="16"/>
+      <c r="M417" s="16"/>
+      <c r="N417" s="17"/>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A418" s="13"/>
+      <c r="B418" s="14"/>
+      <c r="C418" s="14"/>
+      <c r="D418" s="14"/>
+      <c r="E418" s="14"/>
+      <c r="F418" s="14"/>
+      <c r="G418" s="14"/>
+      <c r="H418" s="14"/>
+      <c r="I418" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J418" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K418" s="16"/>
+      <c r="L418" s="16"/>
+      <c r="M418" s="16"/>
+      <c r="N418" s="17"/>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A419" s="13"/>
+      <c r="B419" s="14"/>
+      <c r="C419" s="14"/>
+      <c r="D419" s="14"/>
+      <c r="E419" s="14"/>
+      <c r="F419" s="14"/>
+      <c r="G419" s="14"/>
+      <c r="H419" s="14"/>
+      <c r="I419" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J419" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K419" s="16"/>
+      <c r="L419" s="16"/>
+      <c r="M419" s="16"/>
+      <c r="N419" s="17"/>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A420" s="13"/>
+      <c r="B420" s="14"/>
+      <c r="C420" s="14"/>
+      <c r="D420" s="14"/>
+      <c r="E420" s="14"/>
+      <c r="F420" s="14"/>
+      <c r="G420" s="14"/>
+      <c r="H420" s="14"/>
+      <c r="I420" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J420" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K420" s="16"/>
+      <c r="L420" s="16"/>
+      <c r="M420" s="16"/>
+      <c r="N420" s="17"/>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A421" s="13"/>
+      <c r="B421" s="14"/>
+      <c r="C421" s="14"/>
+      <c r="D421" s="14"/>
+      <c r="E421" s="14"/>
+      <c r="F421" s="14"/>
+      <c r="G421" s="14"/>
+      <c r="H421" s="14"/>
+      <c r="I421" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J421" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K421" s="16"/>
+      <c r="L421" s="16"/>
+      <c r="M421" s="16"/>
+      <c r="N421" s="17"/>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A422" s="13"/>
+      <c r="B422" s="14"/>
+      <c r="C422" s="14"/>
+      <c r="D422" s="14"/>
+      <c r="E422" s="14"/>
+      <c r="F422" s="14"/>
+      <c r="G422" s="14"/>
+      <c r="H422" s="14"/>
+      <c r="I422" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J422" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K422" s="16"/>
+      <c r="L422" s="16"/>
+      <c r="M422" s="16"/>
+      <c r="N422" s="17"/>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A423" s="13"/>
+      <c r="B423" s="14"/>
+      <c r="C423" s="14"/>
+      <c r="D423" s="14"/>
+      <c r="E423" s="14"/>
+      <c r="F423" s="14"/>
+      <c r="G423" s="14"/>
+      <c r="H423" s="14"/>
+      <c r="I423" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J423" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K423" s="16"/>
+      <c r="L423" s="16"/>
+      <c r="M423" s="16"/>
+      <c r="N423" s="17"/>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A424" s="13"/>
+      <c r="B424" s="14"/>
+      <c r="C424" s="14"/>
+      <c r="D424" s="14"/>
+      <c r="E424" s="14"/>
+      <c r="F424" s="14"/>
+      <c r="G424" s="14"/>
+      <c r="H424" s="14"/>
+      <c r="I424" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J424" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K424" s="16"/>
+      <c r="L424" s="16"/>
+      <c r="M424" s="16"/>
+      <c r="N424" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10319,21 +10717,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J424">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K424" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L424" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M424" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
